--- a/output/yearly_surface_area_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_100_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641155895</v>
+        <v>10.84497642097941</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907221838148</v>
+        <v>37.78907225120684</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.052654523130833</v>
+        <v>4.607341976030281</v>
       </c>
       <c r="C2" t="n">
-        <v>7.669413065576083</v>
+        <v>5.88165049614264</v>
       </c>
       <c r="D2" t="n">
-        <v>20.159207359004</v>
+        <v>22.13939247846982</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.94710879715769</v>
+        <v>15.15327581504952</v>
       </c>
       <c r="C3" t="n">
-        <v>32.5203927031756</v>
+        <v>22.16295442337174</v>
       </c>
       <c r="D3" t="n">
-        <v>80.23823986809181</v>
+        <v>88.26893608883073</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.43832680664636</v>
+        <v>31.84298678724529</v>
       </c>
       <c r="C4" t="n">
-        <v>70.45021525675112</v>
+        <v>69.59511300635214</v>
       </c>
       <c r="D4" t="n">
-        <v>107.6280190688736</v>
+        <v>131.5836448002</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.91433557448583</v>
+        <v>37.92000507653306</v>
       </c>
       <c r="C5" t="n">
-        <v>121.8594337896354</v>
+        <v>125.7864246066226</v>
       </c>
       <c r="D5" t="n">
-        <v>78.80979695841272</v>
+        <v>96.62851779049234</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.63529824230149</v>
+        <v>33.24786775202249</v>
       </c>
       <c r="C6" t="n">
-        <v>144.0606763734727</v>
+        <v>138.1034313041031</v>
       </c>
       <c r="D6" t="n">
-        <v>52.04539104523617</v>
+        <v>58.04288777047993</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.17044855210722</v>
+        <v>23.29589127407256</v>
       </c>
       <c r="C7" t="n">
-        <v>132.5290678393897</v>
+        <v>106.8377121669549</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>41.3816474817073</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>85.86856295194725</v>
+        <v>66.25815255961723</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>46.59374604355361</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>28.96450251839364</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.65182181226662</v>
+        <v>7.658434107969301</v>
       </c>
       <c r="C21" t="n">
-        <v>92.77833947373277</v>
+        <v>92.85851355912777</v>
       </c>
       <c r="D21" t="n">
-        <v>7.65182181226662</v>
+        <v>7.658434107969301</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.970588626601601</v>
+        <v>6.777986150119979</v>
       </c>
       <c r="C2" t="n">
-        <v>9.260826094160162</v>
+        <v>7.203082906058848</v>
       </c>
       <c r="D2" t="n">
-        <v>18.50987121586936</v>
+        <v>33.57380798983242</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.12244072559037</v>
+        <v>15.11400590687965</v>
       </c>
       <c r="C3" t="n">
-        <v>30.95941385342317</v>
+        <v>22.59001467471911</v>
       </c>
       <c r="D3" t="n">
-        <v>77.60224728218913</v>
+        <v>86.2318096025186</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.61776565234527</v>
+        <v>29.96686692442964</v>
       </c>
       <c r="C4" t="n">
-        <v>74.80230282967722</v>
+        <v>61.95024363338223</v>
       </c>
       <c r="D4" t="n">
-        <v>118.8336873651467</v>
+        <v>141.3598884390897</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.79223900626073</v>
+        <v>42.06788912697583</v>
       </c>
       <c r="C5" t="n">
-        <v>125.4673566027424</v>
+        <v>125.5900750657732</v>
       </c>
       <c r="D5" t="n">
-        <v>96.08855655315659</v>
+        <v>117.7115497391926</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.80638438474769</v>
+        <v>41.17744395922398</v>
       </c>
       <c r="C6" t="n">
-        <v>165.3940539867559</v>
+        <v>166.8833652540984</v>
       </c>
       <c r="D6" t="n">
-        <v>61.9472983902695</v>
+        <v>71.16492758544281</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.31502750653876</v>
+        <v>30.9014907388726</v>
       </c>
       <c r="C7" t="n">
-        <v>167.7423944953142</v>
+        <v>148.2193596486622</v>
       </c>
       <c r="D7" t="n">
-        <v>45.45393695892307</v>
+        <v>47.54996830749001</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.86075605691297</v>
+        <v>18.10833640483241</v>
       </c>
       <c r="C8" t="n">
-        <v>125.5900750657732</v>
+        <v>100.9727513817844</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>73.66249374504666</v>
+        <v>57.02187015806322</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56719779780995</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1265,7 +1265,7 @@
         <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.824007988293237</v>
+        <v>7.832457210870727</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7341028492754</v>
+        <v>100.8428865899606</v>
       </c>
       <c r="D21" t="n">
-        <v>8.802008986829893</v>
+        <v>8.811514362229568</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.804493338134643</v>
+        <v>7.421030896401639</v>
       </c>
       <c r="C2" t="n">
-        <v>8.672759219316323</v>
+        <v>4.98335134675681</v>
       </c>
       <c r="D2" t="n">
-        <v>34.42007451089317</v>
+        <v>41.62806615547326</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.93238258159398</v>
+        <v>18.14269757448106</v>
       </c>
       <c r="C3" t="n">
-        <v>32.94254421600172</v>
+        <v>24.81858196335937</v>
       </c>
       <c r="D3" t="n">
-        <v>74.4262934589507</v>
+        <v>90.50732085451345</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.52467954689108</v>
+        <v>28.71612034921921</v>
       </c>
       <c r="C4" t="n">
-        <v>74.9299300312293</v>
+        <v>58.69574999380406</v>
       </c>
       <c r="D4" t="n">
-        <v>127.1549809063426</v>
+        <v>147.6263840352971</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.86587008407924</v>
+        <v>43.31961744989052</v>
       </c>
       <c r="C5" t="n">
-        <v>130.4251825091888</v>
+        <v>119.0859965251381</v>
       </c>
       <c r="D5" t="n">
-        <v>110.0293739534613</v>
+        <v>136.3156687346697</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.40136455125026</v>
+        <v>47.13468902859362</v>
       </c>
       <c r="C6" t="n">
-        <v>178.2343322106</v>
+        <v>181.1727030894106</v>
       </c>
       <c r="D6" t="n">
-        <v>73.37876865851936</v>
+        <v>85.89703363537045</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.33983324105218</v>
+        <v>38.08788393395925</v>
       </c>
       <c r="C7" t="n">
-        <v>196.7275137154971</v>
+        <v>185.888037312908</v>
       </c>
       <c r="D7" t="n">
-        <v>51.38271134486956</v>
+        <v>55.03579455237194</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.78698611037422</v>
+        <v>24.20008090968387</v>
       </c>
       <c r="C8" t="n">
-        <v>166.8136611670968</v>
+        <v>140.2770207213055</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>41.22358610132356</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.97812381306608</v>
+        <v>12.97968639784708</v>
       </c>
       <c r="C9" t="n">
-        <v>106.7218659378537</v>
+        <v>85.64374272767472</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>59.78843518863076</v>
+        <v>48.82722207071512</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91549724863931</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1576,7 +1576,7 @@
         <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.980919236660464</v>
+        <v>7.990756763695808</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7424096949163</v>
+        <v>107.8752163098934</v>
       </c>
       <c r="D21" t="n">
-        <v>9.976149045825581</v>
+        <v>9.98844595461976</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.136904899246812</v>
+        <v>6.777986150119979</v>
       </c>
       <c r="C2" t="n">
-        <v>6.035784885709391</v>
+        <v>3.428262983229862</v>
       </c>
       <c r="D2" t="n">
-        <v>28.24979018970197</v>
+        <v>34.17071059401448</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.63357142660446</v>
+        <v>20.69033286700153</v>
       </c>
       <c r="C3" t="n">
-        <v>48.30689578746431</v>
+        <v>36.14795047036755</v>
       </c>
       <c r="D3" t="n">
-        <v>82.89877614660067</v>
+        <v>99.98118620049517</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.55623434214721</v>
+        <v>20.80323385298991</v>
       </c>
       <c r="C4" t="n">
-        <v>105.3817803215569</v>
+        <v>90.99819470663685</v>
       </c>
       <c r="D4" t="n">
-        <v>122.5476389303124</v>
+        <v>145.35461984767</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.93701358267474</v>
+        <v>26.55627539987623</v>
       </c>
       <c r="C5" t="n">
-        <v>106.4950822181728</v>
+        <v>108.2376843932109</v>
       </c>
       <c r="D5" t="n">
-        <v>73.41018458505526</v>
+        <v>87.96459430051422</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.28433128579986</v>
+        <v>23.62772199810799</v>
       </c>
       <c r="C6" t="n">
-        <v>129.5700802587898</v>
+        <v>122.4052855131966</v>
       </c>
       <c r="D6" t="n">
-        <v>33.81139093426016</v>
+        <v>36.22649028670731</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>15.9897248590678</v>
       </c>
       <c r="C7" t="n">
-        <v>117.3178689097896</v>
+        <v>98.6332466025643</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>78.60853867904211</v>
+        <v>63.08710747490004</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1873,7 +1873,7 @@
         <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.68744437715102</v>
+        <v>3.909319358310799</v>
       </c>
       <c r="C2" t="n">
-        <v>3.216205479112551</v>
+        <v>1.916371518689774</v>
       </c>
       <c r="D2" t="n">
-        <v>19.1754961593487</v>
+        <v>24.68015553706056</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.20927649192059</v>
+        <v>22.65382827549515</v>
       </c>
       <c r="C3" t="n">
-        <v>36.64864179953343</v>
+        <v>25.38308689330128</v>
       </c>
       <c r="D3" t="n">
-        <v>86.85521939471532</v>
+        <v>104.8162936439107</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.56747553525043</v>
+        <v>28.58849314766712</v>
       </c>
       <c r="C4" t="n">
-        <v>115.3367020426195</v>
+        <v>93.06575537178064</v>
       </c>
       <c r="D4" t="n">
-        <v>133.3831883420844</v>
+        <v>158.8320523315702</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.00497515844602</v>
+        <v>29.52606220522283</v>
       </c>
       <c r="C5" t="n">
-        <v>148.1457285708437</v>
+        <v>138.0828146023139</v>
       </c>
       <c r="D5" t="n">
-        <v>93.53601252211487</v>
+        <v>111.722888743287</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.83276839957533</v>
+        <v>28.21641076775758</v>
       </c>
       <c r="C6" t="n">
-        <v>152.6342790746601</v>
+        <v>147.200305531654</v>
       </c>
       <c r="D6" t="n">
-        <v>41.861722109084</v>
+        <v>46.16864928761476</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>15.03153909972291</v>
       </c>
       <c r="C7" t="n">
-        <v>145.6442354204228</v>
+        <v>129.3550775115597</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.79978988825843</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>104.1437964665016</v>
+        <v>83.69890052556181</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>49.36718330805084</v>
+        <v>42.15624642035802</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.906374115198058</v>
+        <v>3.920118583057514</v>
       </c>
       <c r="C2" t="n">
-        <v>12.10200395025043</v>
+        <v>6.499169802113885</v>
       </c>
       <c r="D2" t="n">
-        <v>16.78886749032471</v>
+        <v>22.6067043856913</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.52281386247382</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="C3" t="n">
-        <v>24.15099352447153</v>
+        <v>16.09084487260522</v>
       </c>
       <c r="D3" t="n">
-        <v>82.24100518475531</v>
+        <v>100.2953454658542</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.46836007485052</v>
+        <v>35.67180283380785</v>
       </c>
       <c r="C4" t="n">
-        <v>103.3014569362579</v>
+        <v>78.13337279018666</v>
       </c>
       <c r="D4" t="n">
-        <v>144.4101785561845</v>
+        <v>172.5519764984194</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.37375244234433</v>
+        <v>35.51472320112837</v>
       </c>
       <c r="C5" t="n">
-        <v>180.4206843479576</v>
+        <v>154.0362147963246</v>
       </c>
       <c r="D5" t="n">
-        <v>115.7235106380928</v>
+        <v>138.0582709097077</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.34724525432967</v>
+        <v>33.36862271964485</v>
       </c>
       <c r="C6" t="n">
-        <v>190.1890740052134</v>
+        <v>182.2192461421378</v>
       </c>
       <c r="D6" t="n">
-        <v>57.3586096206199</v>
+        <v>65.28818582782139</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.61339669317178</v>
+        <v>22.39759212468673</v>
       </c>
       <c r="C7" t="n">
-        <v>181.2767683460608</v>
+        <v>167.0237551758056</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>143.7818600254666</v>
+        <v>123.2535155296658</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>82.09374302911826</v>
+        <v>68.67030666895162</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>43.41779222031519</v>
+        <v>38.86248287260999</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.3237968159522</v>
+        <v>2.335577788403162</v>
       </c>
       <c r="C2" t="n">
-        <v>5.744205817548087</v>
+        <v>3.02869166760141</v>
       </c>
       <c r="D2" t="n">
-        <v>11.73483030886212</v>
+        <v>15.80417454296515</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.6209886328985</v>
+        <v>17.69600236904876</v>
       </c>
       <c r="C3" t="n">
-        <v>35.37727852253381</v>
+        <v>21.11248437982766</v>
       </c>
       <c r="D3" t="n">
-        <v>80.57203408753573</v>
+        <v>99.37250262386215</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.08020987877453</v>
+        <v>39.14326271602458</v>
       </c>
       <c r="C4" t="n">
-        <v>98.23465703464009</v>
+        <v>72.90065752655114</v>
       </c>
       <c r="D4" t="n">
-        <v>153.5227607470035</v>
+        <v>183.8980347163998</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.2145293878071</v>
+        <v>36.44738352016284</v>
       </c>
       <c r="C5" t="n">
-        <v>214.2664364518664</v>
+        <v>177.303635386974</v>
       </c>
       <c r="D5" t="n">
-        <v>121.7367153266045</v>
+        <v>145.0532233024663</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.7057220351</v>
+        <v>27.45162930614931</v>
       </c>
       <c r="C6" t="n">
-        <v>224.0809682512218</v>
+        <v>216.2721470116427</v>
       </c>
       <c r="D6" t="n">
-        <v>55.78879504152925</v>
+        <v>62.95358978712248</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>189.7806669602466</v>
+        <v>169.4791061841269</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>102.725171033865</v>
+        <v>88.03822537833271</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>33.05937219280708</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.355212742488098</v>
+        <v>2.561379760379928</v>
       </c>
       <c r="C2" t="n">
-        <v>7.438702355078082</v>
+        <v>7.140251052987052</v>
       </c>
       <c r="D2" t="n">
-        <v>11.34114947945915</v>
+        <v>15.41245720897068</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.4976482750619</v>
+        <v>13.02288329683394</v>
       </c>
       <c r="C3" t="n">
-        <v>28.9173786285898</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D3" t="n">
-        <v>72.94876316405924</v>
+        <v>90.88038498212724</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.96159833300992</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="C4" t="n">
-        <v>94.25268834621504</v>
+        <v>63.60939725355934</v>
       </c>
       <c r="D4" t="n">
-        <v>157.4409158346525</v>
+        <v>189.7433605474853</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.03767593232243</v>
+        <v>45.67581194008286</v>
       </c>
       <c r="C5" t="n">
-        <v>198.8529974951915</v>
+        <v>158.9204096249524</v>
       </c>
       <c r="D5" t="n">
-        <v>143.0160968161541</v>
+        <v>170.676838383308</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.23907308041327</v>
+        <v>35.62271544859552</v>
       </c>
       <c r="C6" t="n">
-        <v>278.9842268635204</v>
+        <v>247.1854187229662</v>
       </c>
       <c r="D6" t="n">
-        <v>74.90833158173589</v>
+        <v>85.61527204425161</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22927129890402</v>
+        <v>15.39085875947725</v>
       </c>
       <c r="C7" t="n">
-        <v>246.4333999815131</v>
+        <v>232.4199332510941</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>43.29801900039708</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>161.7232993205771</v>
+        <v>141.9459918185251</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>66.45155685735384</v>
+        <v>57.79843259212245</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
         <v>21.69662426385451</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.733766445699867</v>
+        <v>1.71118624850219</v>
       </c>
       <c r="C2" t="n">
-        <v>5.268058180988385</v>
+        <v>4.253912802501429</v>
       </c>
       <c r="D2" t="n">
-        <v>8.645270283597412</v>
+        <v>13.11516758103314</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.75995483854504</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="C3" t="n">
-        <v>29.17263303169397</v>
+        <v>21.69171552533328</v>
       </c>
       <c r="D3" t="n">
-        <v>67.27426143351268</v>
+        <v>84.27813167106744</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.88578277560466</v>
+        <v>33.20859784385261</v>
       </c>
       <c r="C4" t="n">
-        <v>87.50120938410971</v>
+        <v>55.64545987670921</v>
       </c>
       <c r="D4" t="n">
-        <v>158.1811536036546</v>
+        <v>193.8657191576177</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.30198704894308</v>
+        <v>50.020045531375</v>
       </c>
       <c r="C5" t="n">
-        <v>194.3615017482623</v>
+        <v>147.1885245592031</v>
       </c>
       <c r="D5" t="n">
-        <v>158.282273617192</v>
+        <v>187.6119862815655</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.39757642915352</v>
+        <v>42.66675522656639</v>
       </c>
       <c r="C6" t="n">
-        <v>304.825789934705</v>
+        <v>264.1313658459704</v>
       </c>
       <c r="D6" t="n">
-        <v>87.74860980557993</v>
+        <v>103.8895238111017</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.55244622005047</v>
+        <v>13.95358012045992</v>
       </c>
       <c r="C7" t="n">
-        <v>302.8465865629433</v>
+        <v>277.8139836000581</v>
       </c>
       <c r="D7" t="n">
-        <v>44.97484407925062</v>
+        <v>48.92736033654828</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>205.533790622591</v>
+        <v>186.4240715594268</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>74.99374363200533</v>
+        <v>66.11874438561416</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
         <v>25.33890824661018</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.470077223884975</v>
+        <v>2.105848825609408</v>
       </c>
       <c r="C2" t="n">
-        <v>10.05113299607885</v>
+        <v>6.002405463764999</v>
       </c>
       <c r="D2" t="n">
-        <v>12.98950387488955</v>
+        <v>16.69461971071701</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.452847733565036</v>
+        <v>8.717919613711677</v>
       </c>
       <c r="C3" t="n">
-        <v>25.01984024272996</v>
+        <v>19.1440802328128</v>
       </c>
       <c r="D3" t="n">
-        <v>60.72600424618645</v>
+        <v>76.63522579350602</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.22738991895354</v>
+        <v>28.00140802052752</v>
       </c>
       <c r="C4" t="n">
-        <v>80.86459490340128</v>
+        <v>54.80312034646545</v>
       </c>
       <c r="D4" t="n">
-        <v>154.0970831539879</v>
+        <v>191.6067176901457</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.41841411512095</v>
+        <v>49.82369599052564</v>
       </c>
       <c r="C5" t="n">
-        <v>180.0279852662589</v>
+        <v>127.9217258633594</v>
       </c>
       <c r="D5" t="n">
-        <v>173.0575765661065</v>
+        <v>206.7806102069845</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.88438442173969</v>
+        <v>51.84413276586557</v>
       </c>
       <c r="C6" t="n">
-        <v>307.522650878271</v>
+        <v>253.1426637923358</v>
       </c>
       <c r="D6" t="n">
-        <v>108.035444366136</v>
+        <v>127.9600140238251</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.64954143177966</v>
+        <v>26.05067533218911</v>
       </c>
       <c r="C7" t="n">
-        <v>360.2778455136775</v>
+        <v>320.5730231108237</v>
       </c>
       <c r="D7" t="n">
-        <v>54.5567016726995</v>
+        <v>60.84479571840032</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>277.5498934676157</v>
+        <v>258.9408657336174</v>
       </c>
       <c r="D8" t="n">
-        <v>36.88426124855267</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>137.7843633002228</v>
+        <v>125.4703018458551</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>50.1084028247572</v>
+        <v>46.6919208139783</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3711,7 +3711,7 @@
         <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>20.39482680802324</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.67690719431156</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.36962016288231</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.291620125890307</v>
+        <v>4.569053815564656</v>
       </c>
       <c r="C2" t="n">
-        <v>9.539642442166256</v>
+        <v>4.738896168399354</v>
       </c>
       <c r="D2" t="n">
-        <v>13.71599717603219</v>
+        <v>18.10637290942392</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.804452280405637</v>
+        <v>1.507964473723101</v>
       </c>
       <c r="C2" t="n">
-        <v>5.868887775987432</v>
+        <v>3.456733666653019</v>
       </c>
       <c r="D2" t="n">
-        <v>9.663342652901354</v>
+        <v>12.28755426635308</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.44226949299657</v>
+        <v>11.83987731321653</v>
       </c>
       <c r="C3" t="n">
-        <v>32.71183350550373</v>
+        <v>23.07597978832128</v>
       </c>
       <c r="D3" t="n">
-        <v>65.91454086313085</v>
+        <v>83.86088889676255</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.95258267722244</v>
+        <v>38.00738062221102</v>
       </c>
       <c r="C4" t="n">
-        <v>113.8051756239945</v>
+        <v>78.29928815220435</v>
       </c>
       <c r="D4" t="n">
-        <v>159.1638830556057</v>
+        <v>196.8649583940916</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.09056713516474</v>
+        <v>30.58144098728815</v>
       </c>
       <c r="C5" t="n">
-        <v>264.7282684501525</v>
+        <v>204.4980467946106</v>
       </c>
       <c r="D5" t="n">
-        <v>157.5214191464007</v>
+        <v>187.0965687368359</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.14091400552181</v>
       </c>
       <c r="C6" t="n">
-        <v>291.5427434962456</v>
+        <v>260.7502267525444</v>
       </c>
       <c r="D6" t="n">
-        <v>83.11966938005622</v>
+        <v>97.52976218299091</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>4.850815406683489</v>
       </c>
       <c r="C7" t="n">
-        <v>195.1704618565616</v>
+        <v>182.0552942755285</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>101.5568912658113</v>
+        <v>92.46099878596459</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.162496759482</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4319,7 +4319,7 @@
         <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
         <v>16.34806277111788</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.626036240139976</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.365873098514571</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.917975161199774</v>
+        <v>5.474225198880215</v>
       </c>
       <c r="C2" t="n">
-        <v>8.748353792543327</v>
+        <v>8.927031874716247</v>
       </c>
       <c r="D2" t="n">
-        <v>25.61477935150353</v>
+        <v>26.61321676672253</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.24101121362598</v>
+        <v>9.709484795000954</v>
       </c>
       <c r="C3" t="n">
-        <v>24.03809253848316</v>
+        <v>11.93805208364121</v>
       </c>
       <c r="D3" t="n">
-        <v>14.65749322440488</v>
+        <v>18.34395585385165</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39710219980645</v>
+        <v>13.39729628853811</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1377703401632</v>
+        <v>70.13878645175836</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576129670565465</v>
+        <v>1.576152504533896</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.930336970727482</v>
+        <v>4.271584261177872</v>
       </c>
       <c r="C2" t="n">
-        <v>3.940735284846697</v>
+        <v>5.619523859108742</v>
       </c>
       <c r="D2" t="n">
-        <v>23.41566449399068</v>
+        <v>32.6863080651933</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.76334205001429</v>
+        <v>15.21708941582556</v>
       </c>
       <c r="C3" t="n">
-        <v>30.34582153826891</v>
+        <v>26.24702487303848</v>
       </c>
       <c r="D3" t="n">
-        <v>32.62838495064275</v>
+        <v>36.26576019487717</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.13283903970958</v>
+        <v>11.39710909860122</v>
       </c>
       <c r="C4" t="n">
-        <v>37.17780381212246</v>
+        <v>18.76119862815655</v>
       </c>
       <c r="D4" t="n">
-        <v>22.75593003673682</v>
+        <v>24.68310078017331</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>39.82655911818034</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43608476835521</v>
+        <v>15.43804916137365</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11710449713959</v>
+        <v>86.12806374240034</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249702056495834</v>
+        <v>3.250115612920768</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.78307481509046</v>
+        <v>3.927972564691488</v>
       </c>
       <c r="C2" t="n">
-        <v>11.18505159448391</v>
+        <v>7.670394813280329</v>
       </c>
       <c r="D2" t="n">
-        <v>27.70786545695773</v>
+        <v>40.61097553387356</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.08731879241574</v>
+        <v>14.98146996680633</v>
       </c>
       <c r="C3" t="n">
-        <v>21.3775562599743</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D3" t="n">
-        <v>43.79085634792898</v>
+        <v>54.0010324720958</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.75142220884308</v>
+        <v>21.65833610338889</v>
       </c>
       <c r="C4" t="n">
-        <v>59.62742856513427</v>
+        <v>45.74158903626739</v>
       </c>
       <c r="D4" t="n">
-        <v>33.97436105316512</v>
+        <v>37.29266829351933</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.65825398793088</v>
+        <v>10.28380720198534</v>
       </c>
       <c r="C5" t="n">
-        <v>40.81616080406115</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D5" t="n">
-        <v>30.82687791334985</v>
+        <v>31.51410130632262</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5319,7 +5319,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72362415525451</v>
+        <v>16.72762174159228</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0141073470525</v>
+        <v>102.0384926237129</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180906038813626</v>
+        <v>4.18190543539807</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.114905539125882</v>
+        <v>4.73398742987812</v>
       </c>
       <c r="C2" t="n">
-        <v>6.58065486156637</v>
+        <v>11.49233862591316</v>
       </c>
       <c r="D2" t="n">
-        <v>24.10779662548467</v>
+        <v>38.10751888804419</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.66025854106837</v>
+        <v>14.11753198706914</v>
       </c>
       <c r="C3" t="n">
-        <v>33.84084336538756</v>
+        <v>27.07660168312703</v>
       </c>
       <c r="D3" t="n">
-        <v>55.10549863937347</v>
+        <v>72.8554971321558</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.74164578952962</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="C4" t="n">
-        <v>56.24530772400401</v>
+        <v>52.60793247976958</v>
       </c>
       <c r="D4" t="n">
-        <v>47.50284441768617</v>
+        <v>54.95627298832795</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.24287689804324</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="C5" t="n">
-        <v>77.14082586119314</v>
+        <v>55.78781329382501</v>
       </c>
       <c r="D5" t="n">
-        <v>35.53926689373454</v>
+        <v>37.18369429834795</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.74719211838983</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>39.44662275663685</v>
+        <v>24.11074186859742</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
         <v>39.88448223273092</v>
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,7 +5557,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
         <v>33.16834618797849</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03904001591463</v>
+        <v>18.04592609836599</v>
       </c>
       <c r="C21" t="n">
-        <v>117.683261056205</v>
+        <v>117.7281845464829</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013013338638211</v>
+        <v>6.015308699455331</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.105488972710914</v>
+        <v>6.194828013797373</v>
       </c>
       <c r="C2" t="n">
-        <v>8.778787971374978</v>
+        <v>8.005170780428491</v>
       </c>
       <c r="D2" t="n">
-        <v>34.85498874387451</v>
+        <v>31.00457424781852</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.17291076913446</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="C3" t="n">
-        <v>27.35639977883737</v>
+        <v>34.67532891399734</v>
       </c>
       <c r="D3" t="n">
-        <v>57.55005042294803</v>
+        <v>80.54749039492957</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.06674314835556</v>
+        <v>19.04197847157113</v>
       </c>
       <c r="C4" t="n">
-        <v>60.07412377056657</v>
+        <v>50.91049069912684</v>
       </c>
       <c r="D4" t="n">
-        <v>55.42849363407067</v>
+        <v>67.92319666601983</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.32217747790898</v>
+        <v>18.11324514335366</v>
       </c>
       <c r="C5" t="n">
-        <v>67.17608666308801</v>
+        <v>57.18680377237672</v>
       </c>
       <c r="D5" t="n">
-        <v>35.44109212330986</v>
+        <v>38.48451000647497</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.3107153006275</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>55.50703345041042</v>
+        <v>38.64158963915446</v>
       </c>
       <c r="D6" t="n">
-        <v>31.79880814055419</v>
+        <v>32.28182801104362</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>24.79305652304895</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
         <v>30.17499743772996</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>18.99190933865455</v>
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.045884900875884</v>
+        <v>7.049339920804027</v>
       </c>
       <c r="C21" t="n">
-        <v>66.05517094571141</v>
+        <v>66.08756175753776</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403678063047428</v>
+        <v>4.405837450502517</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.916592502868026</v>
+        <v>4.857687640613218</v>
       </c>
       <c r="C2" t="n">
-        <v>6.163412087261475</v>
+        <v>5.159084185816988</v>
       </c>
       <c r="D2" t="n">
-        <v>27.98373656185109</v>
+        <v>28.60321936323082</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.03117924682442</v>
+        <v>18.41758693167016</v>
       </c>
       <c r="C3" t="n">
-        <v>31.74972075534185</v>
+        <v>32.50075774909066</v>
       </c>
       <c r="D3" t="n">
-        <v>72.91931073293185</v>
+        <v>87.13010875190442</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.53369520267854</v>
+        <v>23.68760860806704</v>
       </c>
       <c r="C4" t="n">
-        <v>65.39617807528853</v>
+        <v>73.20696281027615</v>
       </c>
       <c r="D4" t="n">
-        <v>72.72197944437823</v>
+        <v>94.38031554776711</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.83254741539708</v>
+        <v>24.29825568010856</v>
       </c>
       <c r="C5" t="n">
-        <v>93.60964359993338</v>
+        <v>79.44793296617314</v>
       </c>
       <c r="D5" t="n">
-        <v>47.66385104118265</v>
+        <v>54.63425974133501</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.28683456055609</v>
+        <v>18.35475507859837</v>
       </c>
       <c r="C6" t="n">
-        <v>85.25300714138454</v>
+        <v>68.870583200618</v>
       </c>
       <c r="D6" t="n">
-        <v>36.38749691020379</v>
+        <v>37.71580155404972</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.00106386316226</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>56.47307319138927</v>
+        <v>39.40538935305847</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>26.78698611037422</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>20.81305133003238</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.262027119557139</v>
+        <v>7.266324718187174</v>
       </c>
       <c r="C21" t="n">
-        <v>75.34353136540533</v>
+        <v>75.38811895119193</v>
       </c>
       <c r="D21" t="n">
-        <v>5.446520339667854</v>
+        <v>5.44974353864038</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.650137964389641</v>
+        <v>3.870049450140927</v>
       </c>
       <c r="C2" t="n">
-        <v>9.561240891659686</v>
+        <v>5.097234080449439</v>
       </c>
       <c r="D2" t="n">
-        <v>26.19990098323463</v>
+        <v>24.76164059651305</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.86780821729195</v>
+        <v>17.48492661263569</v>
       </c>
       <c r="C3" t="n">
-        <v>27.15514149946678</v>
+        <v>25.17691987540945</v>
       </c>
       <c r="D3" t="n">
-        <v>77.96549393276045</v>
+        <v>89.48630324209677</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.4428346345401</v>
+        <v>30.47737573063798</v>
       </c>
       <c r="C4" t="n">
-        <v>73.41116633275949</v>
+        <v>77.15064333823558</v>
       </c>
       <c r="D4" t="n">
-        <v>91.12582190818894</v>
+        <v>114.6985660348591</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.14027641518284</v>
+        <v>30.18874190558942</v>
       </c>
       <c r="C5" t="n">
-        <v>107.7222668484813</v>
+        <v>110.7656847316464</v>
       </c>
       <c r="D5" t="n">
-        <v>63.02820261264524</v>
+        <v>76.10999077173399</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.62521872335175</v>
+        <v>26.20382797405162</v>
       </c>
       <c r="C6" t="n">
-        <v>119.6681729137565</v>
+        <v>99.90460987956394</v>
       </c>
       <c r="D6" t="n">
-        <v>42.74725853831463</v>
+        <v>45.76613272887356</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="C7" t="n">
-        <v>92.28526594690442</v>
+        <v>71.0854060213988</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>51.90500112352886</v>
+        <v>38.30288668118931</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>29.06562253193106</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
         <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.46444285002113</v>
+        <v>7.469567915141912</v>
       </c>
       <c r="C21" t="n">
-        <v>83.97498206273771</v>
+        <v>84.03263904534651</v>
       </c>
       <c r="D21" t="n">
-        <v>6.531387493768489</v>
+        <v>6.535871925749174</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_100_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497642097941</v>
+        <v>10.84497627474395</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907225120684</v>
+        <v>37.78907174165273</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.607341976030281</v>
+        <v>6.849653732529996</v>
       </c>
       <c r="C2" t="n">
-        <v>5.88165049614264</v>
+        <v>5.773658248675491</v>
       </c>
       <c r="D2" t="n">
-        <v>22.13939247846982</v>
+        <v>25.56471021858694</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.15327581504952</v>
+        <v>18.21632865229957</v>
       </c>
       <c r="C3" t="n">
-        <v>22.16295442337174</v>
+        <v>19.57114048416017</v>
       </c>
       <c r="D3" t="n">
-        <v>88.26893608883073</v>
+        <v>77.91149780902687</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.84298678724529</v>
+        <v>37.8287025400381</v>
       </c>
       <c r="C4" t="n">
-        <v>69.59511300635214</v>
+        <v>62.98402396595412</v>
       </c>
       <c r="D4" t="n">
-        <v>131.5836448002</v>
+        <v>89.5942954895639</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.92000507653306</v>
+        <v>49.48008429403926</v>
       </c>
       <c r="C5" t="n">
-        <v>125.7864246066226</v>
+        <v>80.52785544084463</v>
       </c>
       <c r="D5" t="n">
-        <v>96.62851779049234</v>
+        <v>67.32334881872504</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.24786775202249</v>
+        <v>50.55607977789376</v>
       </c>
       <c r="C6" t="n">
-        <v>138.1034313041031</v>
+        <v>78.12846405166543</v>
       </c>
       <c r="D6" t="n">
-        <v>58.04288777047993</v>
+        <v>49.06676851055134</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.29589127407256</v>
+        <v>37.66867766424586</v>
       </c>
       <c r="C7" t="n">
-        <v>106.8377121669549</v>
+        <v>70.60631314172635</v>
       </c>
       <c r="D7" t="n">
-        <v>41.3816474817073</v>
+        <v>40.24380189248525</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>20.5283444958008</v>
       </c>
       <c r="C8" t="n">
-        <v>66.25815255961723</v>
+        <v>48.81740459367264</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>9.207811718130833</v>
       </c>
       <c r="C9" t="n">
-        <v>36.94218436310322</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.658434107969301</v>
+        <v>7.709517437691773</v>
       </c>
       <c r="C21" t="n">
-        <v>92.85851355912777</v>
+        <v>95.40527829143569</v>
       </c>
       <c r="D21" t="n">
-        <v>7.658434107969301</v>
+        <v>8.673207117403244</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.777986150119979</v>
+        <v>7.818638716621598</v>
       </c>
       <c r="C2" t="n">
-        <v>7.203082906058848</v>
+        <v>12.17956201888593</v>
       </c>
       <c r="D2" t="n">
-        <v>33.57380798983242</v>
+        <v>29.71259426902972</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.11400590687965</v>
+        <v>20.62651926622549</v>
       </c>
       <c r="C3" t="n">
-        <v>22.59001467471911</v>
+        <v>21.02412708644545</v>
       </c>
       <c r="D3" t="n">
-        <v>86.2318096025186</v>
+        <v>79.73754853892594</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.96686692442964</v>
+        <v>36.0419217183089</v>
       </c>
       <c r="C4" t="n">
-        <v>61.95024363338223</v>
+        <v>55.632697156554</v>
       </c>
       <c r="D4" t="n">
-        <v>141.3598884390897</v>
+        <v>106.3900352138184</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.06788912697583</v>
+        <v>52.98983233672161</v>
       </c>
       <c r="C5" t="n">
-        <v>125.5900750657732</v>
+        <v>97.56117810952681</v>
       </c>
       <c r="D5" t="n">
-        <v>117.7115497391926</v>
+        <v>81.75504007115315</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.17744395922398</v>
+        <v>59.2101857908294</v>
       </c>
       <c r="C6" t="n">
-        <v>166.8833652540984</v>
+        <v>102.6819741348782</v>
       </c>
       <c r="D6" t="n">
-        <v>71.16492758544281</v>
+        <v>58.40515267334701</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.9014907388726</v>
+        <v>48.62792728675301</v>
       </c>
       <c r="C7" t="n">
-        <v>148.2193596486622</v>
+        <v>90.8479873078871</v>
       </c>
       <c r="D7" t="n">
-        <v>47.54996830749001</v>
+        <v>44.91495746929157</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.10833640483241</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="C8" t="n">
-        <v>100.9727513817844</v>
+        <v>71.09816874155401</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>57.02187015806322</v>
+        <v>46.48280855297372</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.832457210870727</v>
+        <v>7.898694150292878</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8428865899606</v>
+        <v>104.6576974913806</v>
       </c>
       <c r="D21" t="n">
-        <v>8.811514362229568</v>
+        <v>9.873367687866097</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.421030896401639</v>
+        <v>9.788024611340701</v>
       </c>
       <c r="C2" t="n">
-        <v>4.98335134675681</v>
+        <v>9.932341523864981</v>
       </c>
       <c r="D2" t="n">
-        <v>41.62806615547326</v>
+        <v>38.03290606252143</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.14269757448106</v>
+        <v>23.05143609571511</v>
       </c>
       <c r="C3" t="n">
-        <v>24.81858196335937</v>
+        <v>33.8752045350362</v>
       </c>
       <c r="D3" t="n">
-        <v>90.50732085451345</v>
+        <v>83.31601892090556</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.71612034921921</v>
+        <v>37.30543101367455</v>
       </c>
       <c r="C4" t="n">
-        <v>58.69574999380406</v>
+        <v>54.02459441699773</v>
       </c>
       <c r="D4" t="n">
-        <v>147.6263840352971</v>
+        <v>117.6339916705571</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.31961744989052</v>
+        <v>53.28435664799564</v>
       </c>
       <c r="C5" t="n">
-        <v>119.0859965251381</v>
+        <v>98.73927535462298</v>
       </c>
       <c r="D5" t="n">
-        <v>136.3156687346697</v>
+        <v>98.12568303946873</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.13468902859362</v>
+        <v>64.72466264558373</v>
       </c>
       <c r="C6" t="n">
-        <v>181.1727030894106</v>
+        <v>126.4707027564826</v>
       </c>
       <c r="D6" t="n">
-        <v>85.89703363537045</v>
+        <v>67.94479511551327</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.08788393395925</v>
+        <v>58.50921792999716</v>
       </c>
       <c r="C7" t="n">
-        <v>185.888037312908</v>
+        <v>116.0003634906904</v>
       </c>
       <c r="D7" t="n">
-        <v>55.03579455237194</v>
+        <v>50.60418541540184</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.20008090968387</v>
+        <v>40.80634332701867</v>
       </c>
       <c r="C8" t="n">
-        <v>140.2770207213055</v>
+        <v>93.2120357797134</v>
       </c>
       <c r="D8" t="n">
         <v>41.22358610132356</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.97968639784708</v>
+        <v>21.41093568191868</v>
       </c>
       <c r="C9" t="n">
-        <v>85.64374272767472</v>
+        <v>65.67499442329461</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>37.38593432542277</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>48.82722207071512</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.42774856607789</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.990756763695808</v>
+        <v>8.072679323506879</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8752163098934</v>
+        <v>113.0175105290963</v>
       </c>
       <c r="D21" t="n">
-        <v>9.98844595461976</v>
+        <v>11.09993406982196</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.777986150119979</v>
+        <v>8.785660205304707</v>
       </c>
       <c r="C2" t="n">
-        <v>3.428262983229862</v>
+        <v>6.594399329425825</v>
       </c>
       <c r="D2" t="n">
-        <v>34.17071059401448</v>
+        <v>30.76110081716531</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.69033286700153</v>
+        <v>27.15023276094554</v>
       </c>
       <c r="C3" t="n">
-        <v>36.14795047036755</v>
+        <v>47.25151700539899</v>
       </c>
       <c r="D3" t="n">
-        <v>99.98118620049517</v>
+        <v>91.7688666544706</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.80323385298991</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="C4" t="n">
-        <v>90.99819470663685</v>
+        <v>80.40513697781377</v>
       </c>
       <c r="D4" t="n">
-        <v>145.35461984767</v>
+        <v>112.6948189704914</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.55627539987623</v>
+        <v>36.44738352016284</v>
       </c>
       <c r="C5" t="n">
-        <v>108.2376843932109</v>
+        <v>75.57002953439824</v>
       </c>
       <c r="D5" t="n">
-        <v>87.96459430051422</v>
+        <v>67.91239744127311</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.62772199810799</v>
+        <v>36.30699359845555</v>
       </c>
       <c r="C6" t="n">
-        <v>122.4052855131966</v>
+        <v>76.3976428490783</v>
       </c>
       <c r="D6" t="n">
-        <v>36.22649028670731</v>
+        <v>33.32837106377072</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.9897248590678</v>
+        <v>27.008861091534</v>
       </c>
       <c r="C7" t="n">
-        <v>98.6332466025643</v>
+        <v>65.51595129520663</v>
       </c>
       <c r="D7" t="n">
         <v>28.98511922018283</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>14.85384276525424</v>
       </c>
       <c r="C8" t="n">
-        <v>63.08710747490004</v>
+        <v>48.40016181936775</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>28.47068342315751</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.909319358310799</v>
+        <v>5.243514488382214</v>
       </c>
       <c r="C2" t="n">
-        <v>1.916371518689774</v>
+        <v>2.921681167838508</v>
       </c>
       <c r="D2" t="n">
-        <v>24.68015553706056</v>
+        <v>21.21851313188631</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.65382827549515</v>
+        <v>29.56042337487146</v>
       </c>
       <c r="C3" t="n">
-        <v>25.38308689330128</v>
+        <v>36.6584592765759</v>
       </c>
       <c r="D3" t="n">
-        <v>104.8162936439107</v>
+        <v>96.14746141541139</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.58849314766712</v>
+        <v>37.79041437957247</v>
       </c>
       <c r="C4" t="n">
-        <v>93.06575537178064</v>
+        <v>102.1911002827547</v>
       </c>
       <c r="D4" t="n">
-        <v>158.8320523315702</v>
+        <v>130.7668307102666</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.52606220522283</v>
+        <v>39.51534509593412</v>
       </c>
       <c r="C5" t="n">
-        <v>138.0828146023139</v>
+        <v>111.0111216577081</v>
       </c>
       <c r="D5" t="n">
-        <v>111.722888743287</v>
+        <v>85.70657458074656</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.21641076775758</v>
+        <v>43.47178834404877</v>
       </c>
       <c r="C6" t="n">
-        <v>147.200305531654</v>
+        <v>97.16749728012383</v>
       </c>
       <c r="D6" t="n">
-        <v>46.16864928761476</v>
+        <v>41.37870223859457</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.03153909972291</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="C7" t="n">
-        <v>129.3550775115597</v>
+        <v>84.9192129219406</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.760715602071035</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C8" t="n">
-        <v>83.69890052556181</v>
+        <v>62.58641614573416</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>39.82655911818034</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.920118583057514</v>
+        <v>6.497206306705391</v>
       </c>
       <c r="C2" t="n">
-        <v>6.499169802113885</v>
+        <v>4.365832040785565</v>
       </c>
       <c r="D2" t="n">
-        <v>22.6067043856913</v>
+        <v>18.02979658849267</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.95125677215293</v>
+        <v>23.58157985600839</v>
       </c>
       <c r="C3" t="n">
-        <v>16.09084487260522</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D3" t="n">
-        <v>100.2953454658542</v>
+        <v>90.96383353698822</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.67180283380785</v>
+        <v>47.46455625722054</v>
       </c>
       <c r="C4" t="n">
-        <v>78.13337279018666</v>
+        <v>96.56274069430778</v>
       </c>
       <c r="D4" t="n">
-        <v>172.5519764984194</v>
+        <v>147.3838923523482</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.51472320112837</v>
+        <v>47.76202581160733</v>
       </c>
       <c r="C5" t="n">
-        <v>154.0362147963246</v>
+        <v>151.6309329209199</v>
       </c>
       <c r="D5" t="n">
-        <v>138.0582709097077</v>
+        <v>110.1520924164922</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.36862271964485</v>
+        <v>48.66425195181016</v>
       </c>
       <c r="C6" t="n">
-        <v>182.2192461421378</v>
+        <v>135.2858153929147</v>
       </c>
       <c r="D6" t="n">
-        <v>65.28818582782139</v>
+        <v>56.03030497677397</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.39759212468673</v>
+        <v>36.89015173477814</v>
       </c>
       <c r="C7" t="n">
-        <v>167.0237551758056</v>
+        <v>112.5868267230242</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>18.19178495969339</v>
       </c>
       <c r="C8" t="n">
-        <v>123.2535155296658</v>
+        <v>86.61959994569608</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>68.67030666895162</v>
+        <v>57.57655761096267</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.62030998483051</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
         <v>38.86248287260999</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.335577788403162</v>
+        <v>3.811144587886118</v>
       </c>
       <c r="C2" t="n">
-        <v>3.02869166760141</v>
+        <v>1.971349390127595</v>
       </c>
       <c r="D2" t="n">
-        <v>15.80417454296515</v>
+        <v>12.42892593576462</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.69600236904876</v>
+        <v>24.87257808709294</v>
       </c>
       <c r="C3" t="n">
-        <v>21.11248437982766</v>
+        <v>21.64753687864217</v>
       </c>
       <c r="D3" t="n">
-        <v>99.37250262386215</v>
+        <v>88.68617886313562</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.14326271602458</v>
+        <v>52.63345792008</v>
       </c>
       <c r="C4" t="n">
-        <v>72.90065752655114</v>
+        <v>90.87056750508476</v>
       </c>
       <c r="D4" t="n">
-        <v>183.8980347163998</v>
+        <v>158.5257470478452</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.44738352016284</v>
+        <v>50.80544369477245</v>
       </c>
       <c r="C5" t="n">
-        <v>177.303635386974</v>
+        <v>181.3778883595982</v>
       </c>
       <c r="D5" t="n">
-        <v>145.0532233024663</v>
+        <v>119.9695694589603</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.45162930614931</v>
+        <v>43.1095234411817</v>
       </c>
       <c r="C6" t="n">
-        <v>216.2721470116427</v>
+        <v>166.9638685658466</v>
       </c>
       <c r="D6" t="n">
-        <v>62.95358978712248</v>
+        <v>55.02401357992099</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>12.03720860177014</v>
       </c>
       <c r="C7" t="n">
-        <v>169.4791061841269</v>
+        <v>116.8986626400762</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>88.03822537833271</v>
+        <v>70.43058030266617</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
         <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.561379760379928</v>
+        <v>4.358959806855839</v>
       </c>
       <c r="C2" t="n">
-        <v>7.140251052987052</v>
+        <v>5.101161071266427</v>
       </c>
       <c r="D2" t="n">
-        <v>15.41245720897068</v>
+        <v>13.23297730554276</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.02288329683394</v>
+        <v>19.1146278016854</v>
       </c>
       <c r="C3" t="n">
-        <v>16.3902779224005</v>
+        <v>14.27952035826986</v>
       </c>
       <c r="D3" t="n">
-        <v>90.88038498212724</v>
+        <v>79.11413874672922</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.96083756948391</v>
+        <v>50.28511741152163</v>
       </c>
       <c r="C4" t="n">
-        <v>63.60939725355934</v>
+        <v>72.91342024670637</v>
       </c>
       <c r="D4" t="n">
-        <v>189.7433605474853</v>
+        <v>165.4559040921234</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.67581194008286</v>
+        <v>63.34727061652545</v>
       </c>
       <c r="C5" t="n">
-        <v>158.9204096249524</v>
+        <v>176.2728002975148</v>
       </c>
       <c r="D5" t="n">
-        <v>170.676838383308</v>
+        <v>144.7096116059799</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.62271544859552</v>
+        <v>54.05797383894213</v>
       </c>
       <c r="C6" t="n">
-        <v>247.1854187229662</v>
+        <v>223.3966901013617</v>
       </c>
       <c r="D6" t="n">
-        <v>85.61527204425161</v>
+        <v>75.23034482872885</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.39085875947725</v>
+        <v>25.21226279276233</v>
       </c>
       <c r="C7" t="n">
-        <v>232.4199332510941</v>
+        <v>173.2519626115474</v>
       </c>
       <c r="D7" t="n">
-        <v>43.29801900039708</v>
+        <v>41.26187426178919</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>141.9459918185251</v>
+        <v>106.1465617831651</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>57.79843259212245</v>
+        <v>51.69687061022852</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.71118624850219</v>
+        <v>3.32125248346696</v>
       </c>
       <c r="C2" t="n">
-        <v>4.253912802501429</v>
+        <v>2.888301745894116</v>
       </c>
       <c r="D2" t="n">
-        <v>13.11516758103314</v>
+        <v>9.706539551888214</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.34900346109313</v>
+        <v>17.50947030524186</v>
       </c>
       <c r="C3" t="n">
-        <v>21.69171552533328</v>
+        <v>17.06277509980957</v>
       </c>
       <c r="D3" t="n">
-        <v>84.27813167106744</v>
+        <v>73.25310495237576</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.20859784385261</v>
+        <v>45.67777543549135</v>
       </c>
       <c r="C4" t="n">
-        <v>55.64545987670921</v>
+        <v>58.37668198992384</v>
       </c>
       <c r="D4" t="n">
-        <v>193.8657191576177</v>
+        <v>167.4213629960256</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.020045531375</v>
+        <v>70.09678608322227</v>
       </c>
       <c r="C5" t="n">
-        <v>147.1885245592031</v>
+        <v>165.8662746324986</v>
       </c>
       <c r="D5" t="n">
-        <v>187.6119862815655</v>
+        <v>163.0682936753952</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.66675522656639</v>
+        <v>63.47686131348603</v>
       </c>
       <c r="C6" t="n">
-        <v>264.1313658459704</v>
+        <v>253.5854320069512</v>
       </c>
       <c r="D6" t="n">
-        <v>103.8895238111017</v>
+        <v>89.80144425516001</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.95358012045992</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="C7" t="n">
-        <v>277.8139836000581</v>
+        <v>225.5928597157618</v>
       </c>
       <c r="D7" t="n">
-        <v>48.92736033654828</v>
+        <v>46.65166915810418</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>186.4240715594268</v>
+        <v>139.1087409532518</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>66.11874438561416</v>
+        <v>62.34686970589792</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.105848825609408</v>
+        <v>5.621487354517236</v>
       </c>
       <c r="C2" t="n">
-        <v>6.002405463764999</v>
+        <v>4.952917167925158</v>
       </c>
       <c r="D2" t="n">
-        <v>16.69461971071701</v>
+        <v>22.14822820780804</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.717919613711677</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="C3" t="n">
-        <v>19.1440802328128</v>
+        <v>14.15680189523901</v>
       </c>
       <c r="D3" t="n">
-        <v>76.63522579350602</v>
+        <v>65.98326320242812</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.00140802052752</v>
+        <v>39.64100880207771</v>
       </c>
       <c r="C4" t="n">
-        <v>54.80312034646545</v>
+        <v>50.96154157974768</v>
       </c>
       <c r="D4" t="n">
-        <v>191.6067176901457</v>
+        <v>164.0392421548953</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.82369599052564</v>
+        <v>70.21950454625312</v>
       </c>
       <c r="C5" t="n">
-        <v>127.9217258633594</v>
+        <v>139.7517856995335</v>
       </c>
       <c r="D5" t="n">
-        <v>206.7806102069845</v>
+        <v>180.9851892778995</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.84413276586557</v>
+        <v>75.63286138747003</v>
       </c>
       <c r="C6" t="n">
-        <v>253.1426637923358</v>
+        <v>261.2332466230338</v>
       </c>
       <c r="D6" t="n">
-        <v>127.9600140238251</v>
+        <v>112.5033781681633</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.05067533218911</v>
+        <v>41.98051358129786</v>
       </c>
       <c r="C7" t="n">
-        <v>320.5730231108237</v>
+        <v>283.4433249362094</v>
       </c>
       <c r="D7" t="n">
-        <v>60.84479571840032</v>
+        <v>57.25159912085699</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.34347282776614</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="C8" t="n">
-        <v>258.9408657336174</v>
+        <v>203.9482680802324</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>125.4703018458551</v>
+        <v>103.0609287487174</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6919208139783</v>
+        <v>47.83074815090461</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.47420950334699</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>12.29148125717007</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.569053815564656</v>
+        <v>8.478373173875454</v>
       </c>
       <c r="C2" t="n">
-        <v>4.738896168399354</v>
+        <v>3.926009069282995</v>
       </c>
       <c r="D2" t="n">
-        <v>18.10637290942392</v>
+        <v>12.69596131131975</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.507964473723101</v>
+        <v>3.978041697608075</v>
       </c>
       <c r="C2" t="n">
-        <v>3.456733666653019</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="D2" t="n">
-        <v>12.28755426635308</v>
+        <v>16.30093888131404</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.83987731321653</v>
+        <v>19.67913273162732</v>
       </c>
       <c r="C3" t="n">
-        <v>23.07597978832128</v>
+        <v>17.90216938694059</v>
       </c>
       <c r="D3" t="n">
-        <v>83.86088889676255</v>
+        <v>74.66682164649117</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.00738062221102</v>
+        <v>53.9990689766873</v>
       </c>
       <c r="C4" t="n">
-        <v>78.29928815220435</v>
+        <v>74.78954010952202</v>
       </c>
       <c r="D4" t="n">
-        <v>196.8649583940916</v>
+        <v>168.1360753247172</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.58144098728815</v>
+        <v>45.18493808795945</v>
       </c>
       <c r="C5" t="n">
-        <v>204.4980467946106</v>
+        <v>215.8863201638736</v>
       </c>
       <c r="D5" t="n">
-        <v>187.0965687368359</v>
+        <v>165.6453813990431</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.14091400552181</v>
+        <v>26.04282135055514</v>
       </c>
       <c r="C6" t="n">
-        <v>260.7502267525444</v>
+        <v>240.4231405361142</v>
       </c>
       <c r="D6" t="n">
-        <v>97.52976218299091</v>
+        <v>87.90961642907641</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.850815406683489</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>182.0552942755285</v>
+        <v>143.4284308519377</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>92.46099878596459</v>
+        <v>75.93818492349078</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>35.61093447614454</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>22.49183990429443</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.474225198880215</v>
+        <v>7.725372684718151</v>
       </c>
       <c r="C2" t="n">
-        <v>8.927031874716247</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="D2" t="n">
-        <v>26.61321676672253</v>
+        <v>19.6074651492173</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.709484795000954</v>
+        <v>18.00034415736527</v>
       </c>
       <c r="C3" t="n">
-        <v>11.93805208364121</v>
+        <v>9.891108120286615</v>
       </c>
       <c r="D3" t="n">
-        <v>18.34395585385165</v>
+        <v>13.79846398318892</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39729628853811</v>
+        <v>13.39769299950142</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13878645175836</v>
+        <v>70.14086335033099</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576152504533896</v>
+        <v>1.576199176411932</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.271584261177872</v>
+        <v>5.527239574909543</v>
       </c>
       <c r="C2" t="n">
-        <v>5.619523859108742</v>
+        <v>4.345215338996383</v>
       </c>
       <c r="D2" t="n">
-        <v>32.6863080651933</v>
+        <v>19.70662166734622</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.21708941582556</v>
+        <v>23.27232932917064</v>
       </c>
       <c r="C3" t="n">
-        <v>26.24702487303848</v>
+        <v>12.37002107350981</v>
       </c>
       <c r="D3" t="n">
-        <v>36.26576019487717</v>
+        <v>26.93424826601124</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.39710909860122</v>
+        <v>20.76494569252429</v>
       </c>
       <c r="C4" t="n">
-        <v>18.76119862815655</v>
+        <v>15.64709491028566</v>
       </c>
       <c r="D4" t="n">
-        <v>24.68310078017331</v>
+        <v>22.29647211114931</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4896,7 +4896,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43804916137365</v>
+        <v>15.440083542737</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12806374240034</v>
+        <v>86.13941344895379</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250115612920768</v>
+        <v>3.250543903734105</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.927972564691488</v>
+        <v>5.130613502393831</v>
       </c>
       <c r="C2" t="n">
-        <v>7.670394813280329</v>
+        <v>3.798381867730909</v>
       </c>
       <c r="D2" t="n">
-        <v>40.61097553387356</v>
+        <v>15.0668820170758</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.98146996680633</v>
+        <v>20.9455872701057</v>
       </c>
       <c r="C3" t="n">
-        <v>23.61594102565702</v>
+        <v>15.11891464540088</v>
       </c>
       <c r="D3" t="n">
-        <v>54.0010324720958</v>
+        <v>36.44738352016284</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.65833610338889</v>
+        <v>34.45934441906305</v>
       </c>
       <c r="C4" t="n">
-        <v>45.74158903626739</v>
+        <v>24.6703380600181</v>
       </c>
       <c r="D4" t="n">
-        <v>37.29266829351933</v>
+        <v>30.77091829420778</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.28380720198534</v>
+        <v>17.84326452468578</v>
       </c>
       <c r="C5" t="n">
-        <v>22.11386703815941</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="D5" t="n">
-        <v>31.51410130632262</v>
+        <v>30.67961575771283</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72762174159228</v>
+        <v>16.73443134555884</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0384926237129</v>
+        <v>102.0800312079089</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18190543539807</v>
+        <v>5.020329403667652</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.73398742987812</v>
+        <v>5.708862900195202</v>
       </c>
       <c r="C2" t="n">
-        <v>11.49233862591316</v>
+        <v>4.438481370899829</v>
       </c>
       <c r="D2" t="n">
-        <v>38.10751888804419</v>
+        <v>20.74825598155209</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.11753198706914</v>
+        <v>19.0999015861217</v>
       </c>
       <c r="C3" t="n">
-        <v>27.07660168312703</v>
+        <v>14.89802141194535</v>
       </c>
       <c r="D3" t="n">
-        <v>72.8554971321558</v>
+        <v>39.79023445312323</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.41057582902019</v>
+        <v>37.65002445786518</v>
       </c>
       <c r="C4" t="n">
-        <v>52.60793247976958</v>
+        <v>32.16205479112551</v>
       </c>
       <c r="D4" t="n">
-        <v>54.95627298832795</v>
+        <v>41.21082338116835</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.3775562599743</v>
+        <v>35.19565519724816</v>
       </c>
       <c r="C5" t="n">
-        <v>55.78781329382501</v>
+        <v>33.50214040742241</v>
       </c>
       <c r="D5" t="n">
-        <v>37.18369429834795</v>
+        <v>34.92567457858028</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.861655689159212</v>
+        <v>14.97361598517235</v>
       </c>
       <c r="C6" t="n">
-        <v>24.11074186859742</v>
+        <v>21.45413258090555</v>
       </c>
       <c r="D6" t="n">
-        <v>38.64158963915446</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04592609836599</v>
+        <v>18.06485451910963</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7281845464829</v>
+        <v>117.851669958001</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015308699455331</v>
+        <v>6.881849340613194</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.194828013797373</v>
+        <v>6.421611733478386</v>
       </c>
       <c r="C2" t="n">
-        <v>8.005170780428491</v>
+        <v>8.474446183058467</v>
       </c>
       <c r="D2" t="n">
-        <v>31.00457424781852</v>
+        <v>27.57042077836317</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.52848336452105</v>
+        <v>17.31802950291373</v>
       </c>
       <c r="C3" t="n">
-        <v>34.67532891399734</v>
+        <v>15.30544670920778</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54749039492957</v>
+        <v>43.94302724208723</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.04197847157113</v>
+        <v>27.28669569183585</v>
       </c>
       <c r="C4" t="n">
-        <v>50.91049069912684</v>
+        <v>29.39254451744526</v>
       </c>
       <c r="D4" t="n">
-        <v>67.92319666601983</v>
+        <v>44.4015034199705</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.11324514335366</v>
+        <v>28.17615911188346</v>
       </c>
       <c r="C5" t="n">
-        <v>57.18680377237672</v>
+        <v>35.22019888985433</v>
       </c>
       <c r="D5" t="n">
-        <v>38.48451000647497</v>
+        <v>33.99301425954582</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.58618549489336</v>
+        <v>17.26796036999715</v>
       </c>
       <c r="C6" t="n">
-        <v>38.64158963915446</v>
+        <v>26.04282135055514</v>
       </c>
       <c r="D6" t="n">
-        <v>32.28182801104362</v>
+        <v>31.35603992593888</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>17.84620976779852</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="D7" t="n">
         <v>31.02126395879071</v>
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049339920804027</v>
+        <v>7.063514069535384</v>
       </c>
       <c r="C21" t="n">
-        <v>66.08756175753776</v>
+        <v>66.22044440189423</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405837450502517</v>
+        <v>5.297635552151537</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.857687640613218</v>
+        <v>5.510549863937347</v>
       </c>
       <c r="C2" t="n">
-        <v>5.159084185816988</v>
+        <v>7.24529805734146</v>
       </c>
       <c r="D2" t="n">
-        <v>28.60321936323082</v>
+        <v>29.99042886933156</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.41758693167016</v>
+        <v>20.65597169735289</v>
       </c>
       <c r="C3" t="n">
-        <v>32.50075774909066</v>
+        <v>27.17477645355171</v>
       </c>
       <c r="D3" t="n">
-        <v>87.13010875190442</v>
+        <v>57.16226007977053</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.68760860806704</v>
+        <v>31.86851222755571</v>
       </c>
       <c r="C4" t="n">
-        <v>73.20696281027615</v>
+        <v>35.26339578884118</v>
       </c>
       <c r="D4" t="n">
-        <v>94.38031554776711</v>
+        <v>57.80235958293945</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.29825568010856</v>
+        <v>36.25103397931348</v>
       </c>
       <c r="C5" t="n">
-        <v>79.44793296617314</v>
+        <v>47.36932672990861</v>
       </c>
       <c r="D5" t="n">
-        <v>54.63425974133501</v>
+        <v>42.97600575340413</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.35475507859837</v>
+        <v>29.46421209985528</v>
       </c>
       <c r="C6" t="n">
-        <v>68.870583200618</v>
+        <v>44.27682146153116</v>
       </c>
       <c r="D6" t="n">
-        <v>37.71580155404972</v>
+        <v>35.783722072092</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.402197763571703</v>
+        <v>14.9117658798048</v>
       </c>
       <c r="C7" t="n">
-        <v>39.40538935305847</v>
+        <v>29.46421209985527</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.86352137357647</v>
+        <v>21.19593293468863</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.266324718187174</v>
+        <v>7.290933910107363</v>
       </c>
       <c r="C21" t="n">
-        <v>75.38811895119193</v>
+        <v>76.55480605612732</v>
       </c>
       <c r="D21" t="n">
-        <v>5.44974353864038</v>
+        <v>6.379567171343942</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.870049450140927</v>
+        <v>4.932300466135975</v>
       </c>
       <c r="C2" t="n">
-        <v>5.097234080449439</v>
+        <v>3.491094836301658</v>
       </c>
       <c r="D2" t="n">
-        <v>24.76164059651305</v>
+        <v>33.05642694969435</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.48492661263569</v>
+        <v>19.81657741022187</v>
       </c>
       <c r="C3" t="n">
-        <v>25.17691987540945</v>
+        <v>27.82272993835461</v>
       </c>
       <c r="D3" t="n">
-        <v>89.48630324209677</v>
+        <v>67.89276248718816</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.47737573063798</v>
+        <v>36.71834588653496</v>
       </c>
       <c r="C4" t="n">
-        <v>77.15064333823558</v>
+        <v>54.57339138367169</v>
       </c>
       <c r="D4" t="n">
-        <v>114.6985660348591</v>
+        <v>72.92618296686157</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.18874190558942</v>
+        <v>43.31961744989052</v>
       </c>
       <c r="C5" t="n">
-        <v>110.7656847316464</v>
+        <v>57.94765824316799</v>
       </c>
       <c r="D5" t="n">
-        <v>76.10999077173399</v>
+        <v>54.75697820436586</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.20382797405162</v>
+        <v>40.49316580936395</v>
       </c>
       <c r="C6" t="n">
-        <v>99.90460987956394</v>
+        <v>62.02780170201773</v>
       </c>
       <c r="D6" t="n">
-        <v>45.76613272887356</v>
+        <v>41.25794727097221</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.86995163914969</v>
+        <v>26.29022177202533</v>
       </c>
       <c r="C7" t="n">
-        <v>71.0854060213988</v>
+        <v>49.0471335564664</v>
       </c>
       <c r="D7" t="n">
-        <v>37.36924461445059</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>38.30288668118931</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>25.95937279569415</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>32.50468473990763</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.469567915141912</v>
+        <v>7.506809662132081</v>
       </c>
       <c r="C21" t="n">
-        <v>84.03263904534651</v>
+        <v>86.32831111451894</v>
       </c>
       <c r="D21" t="n">
-        <v>6.535871925749174</v>
+        <v>7.506809662132081</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_100_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_100_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497627474395</v>
+        <v>10.84497619332806</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907174165273</v>
+        <v>37.78907145796093</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.849653732529996</v>
+        <v>1.154535300194249</v>
       </c>
       <c r="C2" t="n">
-        <v>5.773658248675491</v>
+        <v>4.82627171407732</v>
       </c>
       <c r="D2" t="n">
-        <v>25.56471021858694</v>
+        <v>16.6042989219263</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.21632865229957</v>
+        <v>10.30835089459151</v>
       </c>
       <c r="C3" t="n">
-        <v>19.57114048416017</v>
+        <v>47.51658888554562</v>
       </c>
       <c r="D3" t="n">
-        <v>77.91149780902687</v>
+        <v>85.07825605002859</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.8287025400381</v>
+        <v>17.15309588860027</v>
       </c>
       <c r="C4" t="n">
-        <v>62.98402396595412</v>
+        <v>118.3359412790935</v>
       </c>
       <c r="D4" t="n">
-        <v>89.5942954895639</v>
+        <v>94.82701075319942</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.48008429403926</v>
+        <v>15.38889526406876</v>
       </c>
       <c r="C5" t="n">
-        <v>80.52785544084463</v>
+        <v>164.2218472278852</v>
       </c>
       <c r="D5" t="n">
-        <v>67.32334881872504</v>
+        <v>50.53546307610458</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.55607977789376</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>78.12846405166543</v>
+        <v>133.8367557814464</v>
       </c>
       <c r="D6" t="n">
-        <v>49.06676851055134</v>
+        <v>29.3032054763588</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.66867766424586</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>70.60631314172635</v>
+        <v>67.3125495939783</v>
       </c>
       <c r="D7" t="n">
-        <v>40.24380189248525</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.5283444958008</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>48.81740459367264</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.207811718130833</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>35.38218726105505</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.709517437691773</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.40527829143569</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.673207117403244</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.818638716621598</v>
+        <v>1.292961726493049</v>
       </c>
       <c r="C2" t="n">
-        <v>12.17956201888593</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="D2" t="n">
-        <v>29.71259426902972</v>
+        <v>19.87351877706818</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.62651926622549</v>
+        <v>7.034222300928396</v>
       </c>
       <c r="C3" t="n">
-        <v>21.02412708644545</v>
+        <v>31.86262174133023</v>
       </c>
       <c r="D3" t="n">
-        <v>79.73754853892594</v>
+        <v>78.92760668292232</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.0419217183089</v>
+        <v>18.58252054598363</v>
       </c>
       <c r="C4" t="n">
-        <v>55.632697156554</v>
+        <v>118.5146193612665</v>
       </c>
       <c r="D4" t="n">
-        <v>106.3900352138184</v>
+        <v>113.7796501836841</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.98983233672161</v>
+        <v>20.19945901487813</v>
       </c>
       <c r="C5" t="n">
-        <v>97.56117810952681</v>
+        <v>193.3797540440155</v>
       </c>
       <c r="D5" t="n">
-        <v>81.75504007115315</v>
+        <v>70.48948516492099</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.2101857908294</v>
+        <v>14.97361598517235</v>
       </c>
       <c r="C6" t="n">
-        <v>102.6819741348782</v>
+        <v>194.8985177424853</v>
       </c>
       <c r="D6" t="n">
-        <v>58.40515267334701</v>
+        <v>37.11202671593793</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.62792728675301</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>90.8479873078871</v>
+        <v>127.3189327729519</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.54217107911827</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>71.09816874155401</v>
+        <v>58.4974369575462</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>46.48280855297372</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>35.01894061048373</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.9631198600619</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>43.93222801734051</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.898694150292878</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.6576974913806</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.873367687866097</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.788024611340701</v>
+        <v>0.7156940763959247</v>
       </c>
       <c r="C2" t="n">
-        <v>9.932341523864981</v>
+        <v>3.163191103083223</v>
       </c>
       <c r="D2" t="n">
-        <v>38.03290606252143</v>
+        <v>13.69832571735575</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.05143609571511</v>
+        <v>6.695519342963246</v>
       </c>
       <c r="C3" t="n">
-        <v>33.8752045350362</v>
+        <v>31.79880814055419</v>
       </c>
       <c r="D3" t="n">
-        <v>83.31601892090556</v>
+        <v>79.32030576462104</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.30543101367455</v>
+        <v>20.01194520336698</v>
       </c>
       <c r="C4" t="n">
-        <v>54.02459441699773</v>
+        <v>115.0942103596706</v>
       </c>
       <c r="D4" t="n">
-        <v>117.6339916705571</v>
+        <v>124.5513859946801</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.28435664799564</v>
+        <v>19.75767254796706</v>
       </c>
       <c r="C5" t="n">
-        <v>98.73927535462298</v>
+        <v>229.8025938715722</v>
       </c>
       <c r="D5" t="n">
-        <v>98.12568303946873</v>
+        <v>78.26983572107697</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.72466264558373</v>
+        <v>11.55222523587222</v>
       </c>
       <c r="C6" t="n">
-        <v>126.4707027564826</v>
+        <v>230.6419881587032</v>
       </c>
       <c r="D6" t="n">
-        <v>67.94479511551327</v>
+        <v>37.51454327467913</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>58.50921792999716</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>116.0003634906904</v>
+        <v>114.0241053620415</v>
       </c>
       <c r="D7" t="n">
-        <v>50.60418541540184</v>
+        <v>32.33876937788993</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>40.80634332701867</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>93.2120357797134</v>
+        <v>43.81049130201391</v>
       </c>
       <c r="D8" t="n">
-        <v>41.22358610132356</v>
+        <v>35.38218726105504</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21.41093568191868</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>65.67499442329461</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>37.38593432542277</v>
+        <v>39.71562162760046</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.42774856607789</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.73990327829938</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>37.98872741583033</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.072679323506879</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113.0175105290963</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09993406982196</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.785660205304707</v>
+        <v>0.9120436172452868</v>
       </c>
       <c r="C2" t="n">
-        <v>6.594399329425825</v>
+        <v>4.347178834404876</v>
       </c>
       <c r="D2" t="n">
-        <v>30.76110081716531</v>
+        <v>13.38318470429252</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.15023276094554</v>
+        <v>4.624031687002478</v>
       </c>
       <c r="C3" t="n">
-        <v>47.25151700539899</v>
+        <v>21.53463589265379</v>
       </c>
       <c r="D3" t="n">
-        <v>91.7688666544706</v>
+        <v>72.51679417419065</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.60201663134832</v>
+        <v>16.66811252270235</v>
       </c>
       <c r="C4" t="n">
-        <v>80.40513697781377</v>
+        <v>97.9283517509151</v>
       </c>
       <c r="D4" t="n">
-        <v>112.6948189704914</v>
+        <v>134.0851379506209</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.44738352016284</v>
+        <v>24.3473430653209</v>
       </c>
       <c r="C5" t="n">
-        <v>75.57002953439824</v>
+        <v>223.3230590235432</v>
       </c>
       <c r="D5" t="n">
-        <v>67.91239744127311</v>
+        <v>100.6536833779043</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.30699359845555</v>
+        <v>17.54972196111598</v>
       </c>
       <c r="C6" t="n">
-        <v>76.3976428490783</v>
+        <v>296.1314322658952</v>
       </c>
       <c r="D6" t="n">
-        <v>33.32837106377072</v>
+        <v>50.4353248102714</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.008861091534</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>65.51595129520663</v>
+        <v>207.1477838483727</v>
       </c>
       <c r="D7" t="n">
-        <v>28.98511922018283</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>48.40016181936775</v>
+        <v>87.87132826861075</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>40.71405904281946</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.32833000604172</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
+        <v>20.03256190515617</v>
+      </c>
+      <c r="D13" t="n">
         <v>23.15451960466103</v>
-      </c>
-      <c r="D13" t="n">
-        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
         <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>45.33318199130072</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.243514488382214</v>
+        <v>0.5527239574909543</v>
       </c>
       <c r="C2" t="n">
-        <v>2.921681167838508</v>
+        <v>2.530945581548277</v>
       </c>
       <c r="D2" t="n">
-        <v>21.21851313188631</v>
+        <v>10.26711749101314</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.56042337487146</v>
+        <v>4.030074325933156</v>
       </c>
       <c r="C3" t="n">
-        <v>36.6584592765759</v>
+        <v>19.57114048416017</v>
       </c>
       <c r="D3" t="n">
-        <v>96.14746141541139</v>
+        <v>67.8976712257094</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.79041437957247</v>
+        <v>13.96241584979814</v>
       </c>
       <c r="C4" t="n">
-        <v>102.1911002827547</v>
+        <v>80.99222210495337</v>
       </c>
       <c r="D4" t="n">
-        <v>130.7668307102666</v>
+        <v>138.6031408855647</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.51534509593412</v>
+        <v>25.89359569950963</v>
       </c>
       <c r="C5" t="n">
-        <v>111.0111216577081</v>
+        <v>214.1437179888356</v>
       </c>
       <c r="D5" t="n">
-        <v>85.70657458074656</v>
+        <v>117.6133749687679</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.47178834404877</v>
+        <v>21.53463589265379</v>
       </c>
       <c r="C6" t="n">
-        <v>97.16749728012383</v>
+        <v>330.7478563176377</v>
       </c>
       <c r="D6" t="n">
-        <v>41.37870223859457</v>
+        <v>60.6994970581718</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.69135567243478</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>84.9192129219406</v>
+        <v>280.7484274880518</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>62.58641614573416</v>
+        <v>130.9307825768759</v>
       </c>
       <c r="D8" t="n">
-        <v>28.78975142703771</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>39.82655911818034</v>
+        <v>44.5968712131156</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
         <v>21.69662426385451</v>
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.28621266575034</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>38.85168364786328</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.497206306705391</v>
+        <v>0.6175193059712437</v>
       </c>
       <c r="C2" t="n">
-        <v>4.365832040785565</v>
+        <v>9.830239762623313</v>
       </c>
       <c r="D2" t="n">
-        <v>18.02979658849267</v>
+        <v>12.82653375598458</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.58157985600839</v>
+        <v>2.999239236474006</v>
       </c>
       <c r="C3" t="n">
-        <v>22.7323680918349</v>
+        <v>14.79984664152067</v>
       </c>
       <c r="D3" t="n">
-        <v>90.96383353698822</v>
+        <v>61.9728238305799</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.46455625722054</v>
+        <v>11.02699021410017</v>
       </c>
       <c r="C4" t="n">
-        <v>96.56274069430778</v>
+        <v>66.00878864273855</v>
       </c>
       <c r="D4" t="n">
-        <v>147.3838923523482</v>
+        <v>138.5138018444782</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.76202581160733</v>
+        <v>24.27371198750239</v>
       </c>
       <c r="C5" t="n">
-        <v>151.6309329209199</v>
+        <v>187.0720250442297</v>
       </c>
       <c r="D5" t="n">
-        <v>110.1520924164922</v>
+        <v>135.4811831860599</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.66425195181016</v>
+        <v>26.64659618866693</v>
       </c>
       <c r="C6" t="n">
-        <v>135.2858153929147</v>
+        <v>335.9403199253991</v>
       </c>
       <c r="D6" t="n">
-        <v>56.03030497677397</v>
+        <v>77.645444181176</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.89015173477814</v>
+        <v>13.59426046070558</v>
       </c>
       <c r="C7" t="n">
-        <v>112.5868267230242</v>
+        <v>361.3558044929405</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>44.91495746929157</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.19178495969339</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>86.61959994569608</v>
+        <v>226.4793778926967</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>39.63806355896497</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>57.57655761096267</v>
+        <v>88.08436752043229</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
         <v>38.86248287260999</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
+        <v>19.66637001147211</v>
+      </c>
+      <c r="D14" t="n">
         <v>16.59349969717959</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.811144587886118</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C2" t="n">
-        <v>1.971349390127595</v>
+        <v>5.504659377711866</v>
       </c>
       <c r="D2" t="n">
-        <v>12.42892593576462</v>
+        <v>9.439504176333081</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.87257808709294</v>
+        <v>4.187153958612646</v>
       </c>
       <c r="C3" t="n">
-        <v>21.64753687864217</v>
+        <v>24.29825568010856</v>
       </c>
       <c r="D3" t="n">
-        <v>88.68617886313562</v>
+        <v>67.176086663088</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.63345792008</v>
+        <v>17.11480772813465</v>
       </c>
       <c r="C4" t="n">
-        <v>90.87056750508476</v>
+        <v>96.7414187764807</v>
       </c>
       <c r="D4" t="n">
-        <v>158.5257470478452</v>
+        <v>139.8921756212407</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.80544369477245</v>
+        <v>15.90431280879833</v>
       </c>
       <c r="C5" t="n">
-        <v>181.3778883595982</v>
+        <v>282.4979018970197</v>
       </c>
       <c r="D5" t="n">
-        <v>119.9695694589603</v>
+        <v>122.0312396378786</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.1095234411817</v>
+        <v>8.412596077690921</v>
       </c>
       <c r="C6" t="n">
-        <v>166.9638685658466</v>
+        <v>307.1201343195298</v>
       </c>
       <c r="D6" t="n">
-        <v>55.02401357992099</v>
+        <v>63.75862290460487</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.03720860177014</v>
+        <v>3.53330998758427</v>
       </c>
       <c r="C7" t="n">
-        <v>116.8986626400762</v>
+        <v>159.2384958811284</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>70.43058030266617</v>
+        <v>64.92297568184156</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
         <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>19.36890045708532</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
+        <v>16.1301147807751</v>
+      </c>
+      <c r="D13" t="n">
         <v>13.52848336452105</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.358959806855839</v>
+        <v>0.3063052837250048</v>
       </c>
       <c r="C2" t="n">
-        <v>5.101161071266427</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="D2" t="n">
-        <v>13.23297730554276</v>
+        <v>7.293403694849554</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1146278016854</v>
+        <v>2.87161203492192</v>
       </c>
       <c r="C3" t="n">
-        <v>14.27952035826986</v>
+        <v>22.81581664669588</v>
       </c>
       <c r="D3" t="n">
-        <v>79.11413874672922</v>
+        <v>59.73934780341841</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.28511741152163</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C4" t="n">
-        <v>72.91342024670637</v>
+        <v>75.6574050800762</v>
       </c>
       <c r="D4" t="n">
-        <v>165.4559040921234</v>
+        <v>135.3996981266073</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.34727061652545</v>
+        <v>15.73250696055514</v>
       </c>
       <c r="C5" t="n">
-        <v>176.2728002975148</v>
+        <v>212.5729216620407</v>
       </c>
       <c r="D5" t="n">
-        <v>144.7096116059799</v>
+        <v>127.6517452446915</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.05797383894213</v>
+        <v>8.372344421816802</v>
       </c>
       <c r="C6" t="n">
-        <v>223.3966901013617</v>
+        <v>302.1691806470131</v>
       </c>
       <c r="D6" t="n">
-        <v>75.23034482872885</v>
+        <v>68.26680836250623</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>2.814670668075606</v>
       </c>
       <c r="C7" t="n">
-        <v>173.2519626115474</v>
+        <v>200.7399165827538</v>
       </c>
       <c r="D7" t="n">
-        <v>41.26187426178919</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>106.1465617831651</v>
+        <v>75.43749359432491</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>25.95250056176443</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>51.69687061022852</v>
+        <v>28.28906009787183</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>12.43874341280708</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.32125248346696</v>
+        <v>0.4790928796724435</v>
       </c>
       <c r="C2" t="n">
-        <v>2.888301745894116</v>
+        <v>4.890085314853362</v>
       </c>
       <c r="D2" t="n">
-        <v>9.706539551888214</v>
+        <v>9.282424543653592</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.50947030524186</v>
+        <v>1.894773069196344</v>
       </c>
       <c r="C3" t="n">
-        <v>17.06277509980957</v>
+        <v>16.74370709592935</v>
       </c>
       <c r="D3" t="n">
-        <v>73.25310495237576</v>
+        <v>52.56768082389546</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.67777543549135</v>
+        <v>8.755226026473055</v>
       </c>
       <c r="C4" t="n">
-        <v>58.37668198992384</v>
+        <v>66.17470400475625</v>
       </c>
       <c r="D4" t="n">
-        <v>167.4213629960256</v>
+        <v>133.42147650255</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.09678608322227</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="C5" t="n">
-        <v>165.8662746324986</v>
+        <v>174.6529165855076</v>
       </c>
       <c r="D5" t="n">
-        <v>163.0682936753952</v>
+        <v>146.6976507070797</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.47686131348603</v>
+        <v>14.36984114706057</v>
       </c>
       <c r="C6" t="n">
-        <v>253.5854320069512</v>
+        <v>321.2887171872197</v>
       </c>
       <c r="D6" t="n">
-        <v>89.80144425516001</v>
+        <v>90.32471578152357</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>225.5928597157618</v>
+        <v>319.6747239614378</v>
       </c>
       <c r="D7" t="n">
-        <v>46.65166915810418</v>
+        <v>42.87881273068369</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>139.1087409532518</v>
+        <v>166.2295212830699</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>62.34686970589792</v>
+        <v>58.13124506386212</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>22.07656062539802</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>23.77302065833652</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.621487354517236</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C2" t="n">
-        <v>4.952917167925158</v>
+        <v>7.718500450788423</v>
       </c>
       <c r="D2" t="n">
-        <v>22.14822820780804</v>
+        <v>12.92667202181775</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.44641746799181</v>
+        <v>1.737693436516855</v>
       </c>
       <c r="C3" t="n">
-        <v>14.15680189523901</v>
+        <v>17.81381209355838</v>
       </c>
       <c r="D3" t="n">
-        <v>65.98326320242812</v>
+        <v>48.19399480147592</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.64100880207771</v>
+        <v>6.266495596207391</v>
       </c>
       <c r="C4" t="n">
-        <v>50.96154157974768</v>
+        <v>53.92249265575607</v>
       </c>
       <c r="D4" t="n">
-        <v>164.0392421548953</v>
+        <v>129.8862030195573</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.21950454625312</v>
+        <v>15.2661768010379</v>
       </c>
       <c r="C5" t="n">
-        <v>139.7517856995335</v>
+        <v>149.1765636603029</v>
       </c>
       <c r="D5" t="n">
-        <v>180.9851892778995</v>
+        <v>157.6932249946439</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>75.63286138747003</v>
+        <v>18.23400011097601</v>
       </c>
       <c r="C6" t="n">
-        <v>261.2332466230338</v>
+        <v>302.7729554851249</v>
       </c>
       <c r="D6" t="n">
-        <v>112.5033781681633</v>
+        <v>112.1813649211703</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.98051358129786</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>283.4433249362094</v>
+        <v>384.651695767013</v>
       </c>
       <c r="D7" t="n">
-        <v>57.25159912085699</v>
+        <v>55.87420709179872</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>203.9482680802324</v>
+        <v>283.8085350821892</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>103.0609287487174</v>
+        <v>123.473427015417</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>23.96249796525614</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>47.83074815090461</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>27.47420950334699</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>12.29148125717007</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>7.166758241001715</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.478373173875454</v>
+        <v>5.40157586876595</v>
       </c>
       <c r="C2" t="n">
-        <v>3.926009069282995</v>
+        <v>25.7316073283089</v>
       </c>
       <c r="D2" t="n">
-        <v>12.69596131131975</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.978041697608075</v>
+        <v>0.3023782929080176</v>
       </c>
       <c r="C2" t="n">
-        <v>2.773437264497239</v>
+        <v>11.11632925518663</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30093888131404</v>
+        <v>10.53906160508951</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.67913273162732</v>
+        <v>1.629701189049706</v>
       </c>
       <c r="C3" t="n">
-        <v>17.90216938694059</v>
+        <v>23.29687302177681</v>
       </c>
       <c r="D3" t="n">
-        <v>74.66682164649117</v>
+        <v>47.07971115715579</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.9990689766873</v>
+        <v>4.837070938824034</v>
       </c>
       <c r="C4" t="n">
-        <v>74.78954010952202</v>
+        <v>49.50659148205391</v>
       </c>
       <c r="D4" t="n">
-        <v>168.1360753247172</v>
+        <v>124.0281144683165</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.18493808795945</v>
+        <v>12.98361338866407</v>
       </c>
       <c r="C5" t="n">
-        <v>215.8863201638736</v>
+        <v>125.8600556844411</v>
       </c>
       <c r="D5" t="n">
-        <v>165.6453813990431</v>
+        <v>166.1362552511665</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.04282135055514</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="C6" t="n">
-        <v>240.4231405361142</v>
+        <v>276.6496308228215</v>
       </c>
       <c r="D6" t="n">
-        <v>87.90961642907641</v>
+        <v>129.288318667671</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.204465564390594</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>143.4284308519377</v>
+        <v>406.5103084020683</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>70.48653992180824</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.169662426385451</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>75.93818492349078</v>
+        <v>380.0247188368978</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>36.49843440078366</v>
+        <v>214.2202943097667</v>
       </c>
       <c r="D9" t="n">
-        <v>20.96718571959912</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49183990429443</v>
+        <v>83.70380926408306</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.725372684718151</v>
+        <v>4.107632394568655</v>
       </c>
       <c r="C2" t="n">
-        <v>3.553926689373453</v>
+        <v>12.93059901263474</v>
       </c>
       <c r="D2" t="n">
-        <v>19.6074651492173</v>
+        <v>23.02296541229195</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.00034415736527</v>
+        <v>8.70810213666921</v>
       </c>
       <c r="C3" t="n">
-        <v>9.891108120286615</v>
+        <v>50.80544369477244</v>
       </c>
       <c r="D3" t="n">
-        <v>13.79846398318892</v>
+        <v>10.98575681052181</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.63749841742144</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>45.69544689416779</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39769299950142</v>
+        <v>11.67592784988708</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14086335033099</v>
+        <v>59.93642962942037</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576199176411932</v>
+        <v>0.7783951899924724</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.527239574909543</v>
+        <v>2.304161861867264</v>
       </c>
       <c r="C2" t="n">
-        <v>4.345215338996383</v>
+        <v>5.400594121061704</v>
       </c>
       <c r="D2" t="n">
-        <v>19.70662166734622</v>
+        <v>33.18307240354219</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.27232932917064</v>
+        <v>12.19330648674539</v>
       </c>
       <c r="C3" t="n">
-        <v>12.37002107350981</v>
+        <v>50.65818153913542</v>
       </c>
       <c r="D3" t="n">
-        <v>26.93424826601124</v>
+        <v>28.4854096387212</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.76494569252429</v>
+        <v>10.60582044897829</v>
       </c>
       <c r="C4" t="n">
-        <v>15.64709491028566</v>
+        <v>81.77074803442109</v>
       </c>
       <c r="D4" t="n">
-        <v>22.29647211114931</v>
+        <v>20.02470792352219</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.06307819944583</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.18020927588745</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.440083542737</v>
+        <v>13.61936937382206</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13941344895379</v>
+        <v>73.70482249362524</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250543903734105</v>
+        <v>1.602278749861418</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.130613502393831</v>
+        <v>3.195588777323368</v>
       </c>
       <c r="C2" t="n">
-        <v>3.798381867730909</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="D2" t="n">
-        <v>15.0668820170758</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.9455872701057</v>
+        <v>9.797842088383169</v>
       </c>
       <c r="C3" t="n">
-        <v>15.11891464540088</v>
+        <v>32.41240045570844</v>
       </c>
       <c r="D3" t="n">
-        <v>36.44738352016284</v>
+        <v>48.41979677345269</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.45934441906305</v>
+        <v>18.19963894132737</v>
       </c>
       <c r="C4" t="n">
-        <v>24.6703380600181</v>
+        <v>108.8277147634632</v>
       </c>
       <c r="D4" t="n">
-        <v>30.77091829420778</v>
+        <v>29.5967480399286</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.84326452468578</v>
+        <v>9.522952731194062</v>
       </c>
       <c r="C5" t="n">
-        <v>18.77592484372025</v>
+        <v>89.70719647555231</v>
       </c>
       <c r="D5" t="n">
-        <v>30.67961575771283</v>
+        <v>27.39076094848602</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>10.70694046251572</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.08056973167303</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.60177995163684</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73443134555884</v>
+        <v>14.81376457512306</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0800312079089</v>
+        <v>87.23661360905805</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020329403667652</v>
+        <v>2.468960762520511</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.708862900195202</v>
+        <v>2.614394136409256</v>
       </c>
       <c r="C2" t="n">
-        <v>4.438481370899829</v>
+        <v>5.169883410563703</v>
       </c>
       <c r="D2" t="n">
-        <v>20.74825598155209</v>
+        <v>33.00930305989051</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.0999015861217</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C3" t="n">
-        <v>14.89802141194535</v>
+        <v>23.74847696573034</v>
       </c>
       <c r="D3" t="n">
-        <v>39.79023445312323</v>
+        <v>62.77294820954106</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.65002445786518</v>
+        <v>18.72291046769092</v>
       </c>
       <c r="C4" t="n">
-        <v>32.16205479112551</v>
+        <v>92.31275488262334</v>
       </c>
       <c r="D4" t="n">
-        <v>41.21082338116835</v>
+        <v>45.97131799906114</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.19565519724816</v>
+        <v>18.33413837680919</v>
       </c>
       <c r="C5" t="n">
-        <v>33.50214040742241</v>
+        <v>150.9682532205533</v>
       </c>
       <c r="D5" t="n">
-        <v>34.92567457858028</v>
+        <v>31.93134408062751</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.97361598517235</v>
+        <v>8.734609324683873</v>
       </c>
       <c r="C6" t="n">
-        <v>21.45413258090555</v>
+        <v>79.98004022187492</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>40.84561323518855</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06485451910963</v>
+        <v>16.03064157741519</v>
       </c>
       <c r="C21" t="n">
-        <v>117.851669958001</v>
+        <v>100.4024393532846</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881849340613194</v>
+        <v>3.374871911034776</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.421611733478386</v>
+        <v>2.346377013149877</v>
       </c>
       <c r="C2" t="n">
-        <v>8.474446183058467</v>
+        <v>7.536877125502762</v>
       </c>
       <c r="D2" t="n">
-        <v>27.57042077836317</v>
+        <v>29.59772978763284</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.31802950291373</v>
+        <v>9.576948854927634</v>
       </c>
       <c r="C3" t="n">
-        <v>15.30544670920778</v>
+        <v>21.67208057124834</v>
       </c>
       <c r="D3" t="n">
-        <v>43.94302724208723</v>
+        <v>73.17947387455725</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.28669569183585</v>
+        <v>19.41209735607218</v>
       </c>
       <c r="C4" t="n">
-        <v>29.39254451744526</v>
+        <v>74.82782826998763</v>
       </c>
       <c r="D4" t="n">
-        <v>44.4015034199705</v>
+        <v>64.82185566830415</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.17615911188346</v>
+        <v>22.87472150895069</v>
       </c>
       <c r="C5" t="n">
-        <v>35.22019888985433</v>
+        <v>160.8102739556276</v>
       </c>
       <c r="D5" t="n">
-        <v>33.99301425954582</v>
+        <v>39.85895679242051</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.26796036999715</v>
+        <v>16.30192062901829</v>
       </c>
       <c r="C6" t="n">
-        <v>26.04282135055514</v>
+        <v>157.987749305918</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>36.38749691020379</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.707300315414209</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>16.88802400845363</v>
+        <v>64.19844587610741</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>38.71718421238145</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.13308538608361</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>43.61021477034756</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.063514069535384</v>
+        <v>17.26379197179066</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22044440189423</v>
+        <v>113.0778374152288</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297635552151537</v>
+        <v>4.315947992947666</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.510549863937347</v>
+        <v>2.448478774391545</v>
       </c>
       <c r="C2" t="n">
-        <v>7.24529805734146</v>
+        <v>18.06219426273282</v>
       </c>
       <c r="D2" t="n">
-        <v>29.99042886933156</v>
+        <v>30.16125296987051</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.65597169735289</v>
+        <v>8.659014751456867</v>
       </c>
       <c r="C3" t="n">
-        <v>27.17477645355171</v>
+        <v>25.37817815478005</v>
       </c>
       <c r="D3" t="n">
-        <v>57.16226007977053</v>
+        <v>78.43182409227768</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.86851222755571</v>
+        <v>18.78672406846696</v>
       </c>
       <c r="C4" t="n">
-        <v>35.26339578884118</v>
+        <v>64.56660126519998</v>
       </c>
       <c r="D4" t="n">
-        <v>57.80235958293945</v>
+        <v>83.31503717320132</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.25103397931348</v>
+        <v>25.50089661781091</v>
       </c>
       <c r="C5" t="n">
-        <v>47.36932672990861</v>
+        <v>148.2684470338746</v>
       </c>
       <c r="D5" t="n">
-        <v>42.97600575340413</v>
+        <v>51.66447293598841</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.46421209985528</v>
+        <v>22.78243722475149</v>
       </c>
       <c r="C6" t="n">
-        <v>44.27682146153116</v>
+        <v>203.1501071966798</v>
       </c>
       <c r="D6" t="n">
-        <v>35.783722072092</v>
+        <v>39.68813269188156</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.9117658798048</v>
+        <v>12.99539436111503</v>
       </c>
       <c r="C7" t="n">
-        <v>29.46421209985527</v>
+        <v>137.7990895157865</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>38.44720359371359</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>21.19593293468863</v>
+        <v>51.32086123950201</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>42.99073196896783</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.40561033723673</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.290933910107363</v>
+        <v>17.62630068951949</v>
       </c>
       <c r="C21" t="n">
-        <v>76.55480605612732</v>
+        <v>125.1467348955884</v>
       </c>
       <c r="D21" t="n">
-        <v>6.379567171343942</v>
+        <v>5.287890206855846</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.932300466135975</v>
+        <v>2.297289627937536</v>
       </c>
       <c r="C2" t="n">
-        <v>3.491094836301658</v>
+        <v>11.84871304255475</v>
       </c>
       <c r="D2" t="n">
-        <v>33.05642694969435</v>
+        <v>24.33850733598268</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.81657741022187</v>
+        <v>11.8349685746953</v>
       </c>
       <c r="C3" t="n">
-        <v>27.82272993835461</v>
+        <v>46.6624683828509</v>
       </c>
       <c r="D3" t="n">
-        <v>67.89276248718816</v>
+        <v>83.77744034190157</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.71834588653496</v>
+        <v>12.25221134900019</v>
       </c>
       <c r="C4" t="n">
-        <v>54.57339138367169</v>
+        <v>111.814191279782</v>
       </c>
       <c r="D4" t="n">
-        <v>72.92618296686157</v>
+        <v>73.48774265369074</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.31961744989052</v>
+        <v>12.81180754042088</v>
       </c>
       <c r="C5" t="n">
-        <v>57.94765824316799</v>
+        <v>121.3931036301181</v>
       </c>
       <c r="D5" t="n">
-        <v>54.75697820436586</v>
+        <v>38.09181092477625</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.49316580936395</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>62.02780170201773</v>
+        <v>90.72723234026475</v>
       </c>
       <c r="D6" t="n">
-        <v>41.25794727097221</v>
+        <v>25.318291544821</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.29022177202533</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>49.0471335564664</v>
+        <v>36.05173919535137</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>26.40999499194344</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>29.75873641112932</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.506809662132081</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.32831111451894</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.506809662132081</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
